--- a/基本数据.xlsx
+++ b/基本数据.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup\Documents\paike\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\paike\github_upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="各班任课" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="118">
   <si>
     <t>班级</t>
   </si>
@@ -116,6 +116,9 @@
     <t>张懿</t>
   </si>
   <si>
+    <t>说明：班级名格式要统一，支持701班，七一班，七(1)班，七年级1班等</t>
+  </si>
+  <si>
     <t>七二班</t>
   </si>
   <si>
@@ -128,6 +131,9 @@
     <t>李非非</t>
   </si>
   <si>
+    <t>班级没有的课程留空</t>
+  </si>
+  <si>
     <t>七三班</t>
   </si>
   <si>
@@ -269,6 +275,9 @@
     <t>九四班</t>
   </si>
   <si>
+    <t>说明：班级名格式要统一。支持701班，七一班，七(1)班，七年级1班等格式</t>
+  </si>
+  <si>
     <t>时间段</t>
   </si>
   <si>
@@ -311,10 +320,16 @@
     <t>第2节</t>
   </si>
   <si>
+    <t>说明：可以增减节次，也可以增加星期，比如有的学校周六、周天也上课，也是可以的。如果有一个或多个班周六也上课</t>
+  </si>
+  <si>
     <t>09:05-09:45</t>
   </si>
   <si>
     <t>第3节</t>
+  </si>
+  <si>
+    <t>，那么上课的星期数请增至星期六，总之取最多上课天数。</t>
   </si>
   <si>
     <t>10:15-10:55</t>
@@ -387,7 +402,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -413,6 +428,13 @@
       <color rgb="FF080000"/>
       <name val="黑体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -961,155 +983,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1125,19 +1147,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1147,37 +1169,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1518,781 +1537,787 @@
   <dimension ref="A1:X30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="18.2571428571429" style="6" customWidth="1"/>
-    <col min="2" max="17" width="8.42857142857143" style="6" customWidth="1"/>
-    <col min="18" max="18" width="8.85714285714286" style="6" customWidth="1"/>
-    <col min="19" max="19" width="8.57142857142857" style="6" customWidth="1"/>
-    <col min="20" max="16384" width="9.14285714285714" style="6"/>
+    <col min="1" max="1" width="18.2571428571429" style="7" customWidth="1"/>
+    <col min="2" max="17" width="8.42857142857143" style="7" customWidth="1"/>
+    <col min="18" max="18" width="8.85714285714286" style="7" customWidth="1"/>
+    <col min="19" max="19" width="8.57142857142857" style="7" customWidth="1"/>
+    <col min="20" max="16384" width="9.14285714285714" style="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="46.5" customHeight="1" spans="1:24">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="V2" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="3" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="A3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="11" t="s">
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="O3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="12" t="s">
+      <c r="F8" s="11"/>
+      <c r="G8" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A9" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A4" s="9" t="s">
+      <c r="L9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" s="19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q12" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A13" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q13" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q14" s="18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A15" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="12" t="s">
+      <c r="D15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A6" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="P6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" s="19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A7" s="9" t="s">
+      <c r="L15" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="P15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="P7" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="10" t="s">
+      <c r="Q15" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A9" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="P9" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q9" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A10" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q10" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A11" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q11" s="20" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A12" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="M12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O12" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="P12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q12" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A13" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q13" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A14" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="N14" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="O14" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="P14" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q14" s="19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A15" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q15" s="17" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="16" ht="33.95" customHeight="1" spans="1:24">
-      <c r="R16" s="21"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="23"/>
+      <c r="R16" s="20"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="22"/>
     </row>
     <row r="17" ht="33.95" customHeight="1" spans="18:23">
-      <c r="R17" s="15"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="W17" s="16"/>
+      <c r="R17" s="14"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="W17" s="15"/>
     </row>
     <row r="18" ht="33.95" customHeight="1" spans="18:23">
-      <c r="R18" s="15"/>
+      <c r="R18" s="14"/>
     </row>
     <row r="19" ht="33.95" customHeight="1" spans="18:23">
-      <c r="R19" s="15"/>
+      <c r="R19" s="14"/>
     </row>
     <row r="20" ht="33.95" customHeight="1"/>
     <row r="21" ht="33.95" customHeight="1"/>
@@ -2331,773 +2356,779 @@
   <dimension ref="A1:W29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="18.2571428571429" style="6" customWidth="1"/>
-    <col min="2" max="17" width="8.42857142857143" style="6" customWidth="1"/>
-    <col min="18" max="18" width="8.85714285714286" style="6" customWidth="1"/>
-    <col min="19" max="19" width="8.57142857142857" style="6" customWidth="1"/>
-    <col min="20" max="16384" width="9.14285714285714" style="6"/>
+    <col min="1" max="1" width="18.2571428571429" style="7" customWidth="1"/>
+    <col min="2" max="17" width="8.42857142857143" style="7" customWidth="1"/>
+    <col min="18" max="18" width="8.85714285714286" style="7" customWidth="1"/>
+    <col min="19" max="19" width="8.57142857142857" style="7" customWidth="1"/>
+    <col min="20" max="16384" width="9.14285714285714" style="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="46.5" customHeight="1" spans="1:23">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>11</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>12</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="11">
         <v>12</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <v>3</v>
-      </c>
-      <c r="H2" s="11">
-        <v>3</v>
-      </c>
-      <c r="I2" s="12">
-        <v>3</v>
-      </c>
-      <c r="J2" s="12">
-        <v>3</v>
-      </c>
-      <c r="K2" s="12">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11">
+        <v>3</v>
+      </c>
+      <c r="H2" s="12">
+        <v>3</v>
+      </c>
+      <c r="I2" s="13">
+        <v>3</v>
+      </c>
+      <c r="J2" s="13">
+        <v>3</v>
+      </c>
+      <c r="K2" s="13">
         <v>2</v>
       </c>
-      <c r="L2" s="11">
-        <v>1</v>
-      </c>
-      <c r="M2" s="10">
-        <v>1</v>
-      </c>
-      <c r="N2" s="11">
-        <v>1</v>
-      </c>
-      <c r="O2" s="10">
-        <v>1</v>
-      </c>
-      <c r="P2" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="13">
-        <v>1</v>
+      <c r="L2" s="12">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11">
+        <v>1</v>
+      </c>
+      <c r="N2" s="12">
+        <v>1</v>
+      </c>
+      <c r="O2" s="11">
+        <v>1</v>
+      </c>
+      <c r="P2" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="11">
+        <v>1</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="10">
+      <c r="A3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11">
         <v>11</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="12">
         <v>12</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="11">
         <v>12</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10">
-        <v>3</v>
-      </c>
-      <c r="H3" s="11">
-        <v>3</v>
-      </c>
-      <c r="I3" s="12">
-        <v>3</v>
-      </c>
-      <c r="J3" s="12">
-        <v>3</v>
-      </c>
-      <c r="K3" s="12">
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11">
+        <v>3</v>
+      </c>
+      <c r="H3" s="12">
+        <v>3</v>
+      </c>
+      <c r="I3" s="13">
+        <v>3</v>
+      </c>
+      <c r="J3" s="13">
+        <v>3</v>
+      </c>
+      <c r="K3" s="13">
         <v>2</v>
       </c>
-      <c r="L3" s="11">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10">
-        <v>1</v>
-      </c>
-      <c r="N3" s="11">
-        <v>1</v>
-      </c>
-      <c r="O3" s="10">
-        <v>1</v>
-      </c>
-      <c r="P3" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="13">
-        <v>1</v>
+      <c r="L3" s="12">
+        <v>1</v>
+      </c>
+      <c r="M3" s="11">
+        <v>1</v>
+      </c>
+      <c r="N3" s="12">
+        <v>1</v>
+      </c>
+      <c r="O3" s="11">
+        <v>1</v>
+      </c>
+      <c r="P3" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>1</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="10">
+      <c r="A4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="11">
         <v>11</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="12">
         <v>12</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="11">
         <v>12</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10">
-        <v>3</v>
-      </c>
-      <c r="H4" s="11">
-        <v>3</v>
-      </c>
-      <c r="I4" s="12">
-        <v>3</v>
-      </c>
-      <c r="J4" s="12">
-        <v>3</v>
-      </c>
-      <c r="K4" s="12">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11">
+        <v>3</v>
+      </c>
+      <c r="H4" s="12">
+        <v>3</v>
+      </c>
+      <c r="I4" s="13">
+        <v>3</v>
+      </c>
+      <c r="J4" s="13">
+        <v>3</v>
+      </c>
+      <c r="K4" s="13">
         <v>2</v>
       </c>
-      <c r="L4" s="11">
-        <v>1</v>
-      </c>
-      <c r="M4" s="10">
-        <v>1</v>
-      </c>
-      <c r="N4" s="11">
-        <v>1</v>
-      </c>
-      <c r="O4" s="10">
-        <v>1</v>
-      </c>
-      <c r="P4" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="13">
+      <c r="L4" s="12">
+        <v>1</v>
+      </c>
+      <c r="M4" s="11">
+        <v>1</v>
+      </c>
+      <c r="N4" s="12">
+        <v>1</v>
+      </c>
+      <c r="O4" s="11">
+        <v>1</v>
+      </c>
+      <c r="P4" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="10">
+      <c r="A5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="11">
         <v>11</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="12">
         <v>12</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="11">
         <v>12</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10">
-        <v>3</v>
-      </c>
-      <c r="H5" s="11">
-        <v>3</v>
-      </c>
-      <c r="I5" s="12">
-        <v>3</v>
-      </c>
-      <c r="J5" s="12">
-        <v>3</v>
-      </c>
-      <c r="K5" s="12">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11">
+        <v>3</v>
+      </c>
+      <c r="H5" s="12">
+        <v>3</v>
+      </c>
+      <c r="I5" s="13">
+        <v>3</v>
+      </c>
+      <c r="J5" s="13">
+        <v>3</v>
+      </c>
+      <c r="K5" s="13">
         <v>2</v>
       </c>
-      <c r="L5" s="11">
-        <v>1</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1</v>
-      </c>
-      <c r="N5" s="11">
-        <v>1</v>
-      </c>
-      <c r="O5" s="10">
-        <v>1</v>
-      </c>
-      <c r="P5" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="13">
+      <c r="L5" s="12">
+        <v>1</v>
+      </c>
+      <c r="M5" s="11">
+        <v>1</v>
+      </c>
+      <c r="N5" s="12">
+        <v>1</v>
+      </c>
+      <c r="O5" s="11">
+        <v>1</v>
+      </c>
+      <c r="P5" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A6" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="10">
+      <c r="A6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="11">
         <v>11</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <v>12</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="11">
         <v>12</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10">
-        <v>3</v>
-      </c>
-      <c r="H6" s="11">
-        <v>3</v>
-      </c>
-      <c r="I6" s="12">
-        <v>3</v>
-      </c>
-      <c r="J6" s="12">
-        <v>3</v>
-      </c>
-      <c r="K6" s="12">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11">
+        <v>3</v>
+      </c>
+      <c r="H6" s="12">
+        <v>3</v>
+      </c>
+      <c r="I6" s="13">
+        <v>3</v>
+      </c>
+      <c r="J6" s="13">
+        <v>3</v>
+      </c>
+      <c r="K6" s="13">
         <v>2</v>
       </c>
-      <c r="L6" s="11">
-        <v>1</v>
-      </c>
-      <c r="M6" s="10">
-        <v>1</v>
-      </c>
-      <c r="N6" s="11">
-        <v>1</v>
-      </c>
-      <c r="O6" s="10">
-        <v>1</v>
-      </c>
-      <c r="P6" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="13">
+      <c r="L6" s="12">
+        <v>1</v>
+      </c>
+      <c r="M6" s="11">
+        <v>1</v>
+      </c>
+      <c r="N6" s="12">
+        <v>1</v>
+      </c>
+      <c r="O6" s="11">
+        <v>1</v>
+      </c>
+      <c r="P6" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="10">
+      <c r="A7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="11">
         <v>9</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="12">
         <v>10</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="11">
         <v>10</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="11">
         <v>6</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11">
-        <v>3</v>
-      </c>
-      <c r="H7" s="11">
-        <v>3</v>
-      </c>
-      <c r="I7" s="12">
-        <v>3</v>
-      </c>
-      <c r="J7" s="12">
-        <v>3</v>
-      </c>
-      <c r="K7" s="12">
+      <c r="F7" s="11"/>
+      <c r="G7" s="12">
+        <v>3</v>
+      </c>
+      <c r="H7" s="12">
+        <v>3</v>
+      </c>
+      <c r="I7" s="13">
+        <v>3</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3</v>
+      </c>
+      <c r="K7" s="13">
         <v>2</v>
       </c>
-      <c r="L7" s="11">
-        <v>1</v>
-      </c>
-      <c r="M7" s="10">
-        <v>1</v>
-      </c>
-      <c r="N7" s="11">
-        <v>1</v>
-      </c>
-      <c r="O7" s="10">
-        <v>1</v>
-      </c>
-      <c r="P7" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="13">
+      <c r="L7" s="12">
+        <v>1</v>
+      </c>
+      <c r="M7" s="11">
+        <v>1</v>
+      </c>
+      <c r="N7" s="12">
+        <v>1</v>
+      </c>
+      <c r="O7" s="11">
+        <v>1</v>
+      </c>
+      <c r="P7" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="10">
+      <c r="A8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="11">
         <v>9</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="12">
         <v>10</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="11">
         <v>10</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="11">
         <v>6</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11">
-        <v>3</v>
-      </c>
-      <c r="H8" s="11">
-        <v>3</v>
-      </c>
-      <c r="I8" s="12">
-        <v>3</v>
-      </c>
-      <c r="J8" s="12">
-        <v>3</v>
-      </c>
-      <c r="K8" s="12">
+      <c r="F8" s="11"/>
+      <c r="G8" s="12">
+        <v>3</v>
+      </c>
+      <c r="H8" s="12">
+        <v>3</v>
+      </c>
+      <c r="I8" s="13">
+        <v>3</v>
+      </c>
+      <c r="J8" s="13">
+        <v>3</v>
+      </c>
+      <c r="K8" s="13">
         <v>2</v>
       </c>
-      <c r="L8" s="11">
-        <v>1</v>
-      </c>
-      <c r="M8" s="10">
-        <v>1</v>
-      </c>
-      <c r="N8" s="11">
-        <v>1</v>
-      </c>
-      <c r="O8" s="10">
-        <v>1</v>
-      </c>
-      <c r="P8" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="13">
+      <c r="L8" s="12">
+        <v>1</v>
+      </c>
+      <c r="M8" s="11">
+        <v>1</v>
+      </c>
+      <c r="N8" s="12">
+        <v>1</v>
+      </c>
+      <c r="O8" s="11">
+        <v>1</v>
+      </c>
+      <c r="P8" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A9" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="10">
+      <c r="A9" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="11">
         <v>9</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <v>10</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="11">
         <v>10</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="11">
         <v>6</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11">
-        <v>3</v>
-      </c>
-      <c r="H9" s="11">
-        <v>3</v>
-      </c>
-      <c r="I9" s="12">
-        <v>3</v>
-      </c>
-      <c r="J9" s="12">
-        <v>3</v>
-      </c>
-      <c r="K9" s="12">
+      <c r="F9" s="11"/>
+      <c r="G9" s="12">
+        <v>3</v>
+      </c>
+      <c r="H9" s="12">
+        <v>3</v>
+      </c>
+      <c r="I9" s="13">
+        <v>3</v>
+      </c>
+      <c r="J9" s="13">
+        <v>3</v>
+      </c>
+      <c r="K9" s="13">
         <v>2</v>
       </c>
-      <c r="L9" s="11">
-        <v>1</v>
-      </c>
-      <c r="M9" s="10">
-        <v>1</v>
-      </c>
-      <c r="N9" s="11">
-        <v>1</v>
-      </c>
-      <c r="O9" s="10">
-        <v>1</v>
-      </c>
-      <c r="P9" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="13">
+      <c r="L9" s="12">
+        <v>1</v>
+      </c>
+      <c r="M9" s="11">
+        <v>1</v>
+      </c>
+      <c r="N9" s="12">
+        <v>1</v>
+      </c>
+      <c r="O9" s="11">
+        <v>1</v>
+      </c>
+      <c r="P9" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A10" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="10">
+      <c r="A10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="11">
         <v>9</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="12">
         <v>10</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="11">
         <v>10</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="11">
         <v>6</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11">
-        <v>3</v>
-      </c>
-      <c r="H10" s="11">
-        <v>3</v>
-      </c>
-      <c r="I10" s="12">
-        <v>3</v>
-      </c>
-      <c r="J10" s="12">
-        <v>3</v>
-      </c>
-      <c r="K10" s="12">
+      <c r="F10" s="11"/>
+      <c r="G10" s="12">
+        <v>3</v>
+      </c>
+      <c r="H10" s="12">
+        <v>3</v>
+      </c>
+      <c r="I10" s="13">
+        <v>3</v>
+      </c>
+      <c r="J10" s="13">
+        <v>3</v>
+      </c>
+      <c r="K10" s="13">
         <v>2</v>
       </c>
-      <c r="L10" s="11">
-        <v>1</v>
-      </c>
-      <c r="M10" s="10">
-        <v>1</v>
-      </c>
-      <c r="N10" s="11">
-        <v>1</v>
-      </c>
-      <c r="O10" s="10">
-        <v>1</v>
-      </c>
-      <c r="P10" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="13">
+      <c r="L10" s="12">
+        <v>1</v>
+      </c>
+      <c r="M10" s="11">
+        <v>1</v>
+      </c>
+      <c r="N10" s="12">
+        <v>1</v>
+      </c>
+      <c r="O10" s="11">
+        <v>1</v>
+      </c>
+      <c r="P10" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A11" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="10">
+      <c r="A11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="11">
         <v>9</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="12">
         <v>10</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <v>10</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="11">
         <v>6</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11">
-        <v>3</v>
-      </c>
-      <c r="H11" s="11">
-        <v>3</v>
-      </c>
-      <c r="I11" s="12">
-        <v>3</v>
-      </c>
-      <c r="J11" s="12">
-        <v>3</v>
-      </c>
-      <c r="K11" s="12">
+      <c r="F11" s="11"/>
+      <c r="G11" s="12">
+        <v>3</v>
+      </c>
+      <c r="H11" s="12">
+        <v>3</v>
+      </c>
+      <c r="I11" s="13">
+        <v>3</v>
+      </c>
+      <c r="J11" s="13">
+        <v>3</v>
+      </c>
+      <c r="K11" s="13">
         <v>2</v>
       </c>
-      <c r="L11" s="11">
-        <v>1</v>
-      </c>
-      <c r="M11" s="10">
-        <v>1</v>
-      </c>
-      <c r="N11" s="11">
-        <v>1</v>
-      </c>
-      <c r="O11" s="10">
-        <v>1</v>
-      </c>
-      <c r="P11" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="13">
+      <c r="L11" s="12">
+        <v>1</v>
+      </c>
+      <c r="M11" s="11">
+        <v>1</v>
+      </c>
+      <c r="N11" s="12">
+        <v>1</v>
+      </c>
+      <c r="O11" s="11">
+        <v>1</v>
+      </c>
+      <c r="P11" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="12" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A12" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="A12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="13">
         <v>9</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="12">
         <v>10</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="13">
         <v>10</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="11">
         <v>6</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="11">
         <v>5</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="12">
         <v>4</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="12">
         <v>4</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="12">
-        <v>1</v>
-      </c>
-      <c r="L12" s="11">
-        <v>1</v>
-      </c>
-      <c r="M12" s="12">
-        <v>1</v>
-      </c>
-      <c r="N12" s="10">
-        <v>1</v>
-      </c>
-      <c r="O12" s="12">
-        <v>1</v>
-      </c>
-      <c r="P12" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="14">
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="13">
+        <v>1</v>
+      </c>
+      <c r="L12" s="12">
+        <v>1</v>
+      </c>
+      <c r="M12" s="13">
+        <v>1</v>
+      </c>
+      <c r="N12" s="11">
+        <v>1</v>
+      </c>
+      <c r="O12" s="13">
+        <v>1</v>
+      </c>
+      <c r="P12" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A13" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="A13" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="13">
         <v>9</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="12">
         <v>10</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <v>10</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="11">
         <v>6</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="11">
         <v>5</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="12">
         <v>4</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="12">
         <v>4</v>
       </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="12">
-        <v>1</v>
-      </c>
-      <c r="L13" s="11">
-        <v>1</v>
-      </c>
-      <c r="M13" s="12">
-        <v>1</v>
-      </c>
-      <c r="N13" s="10">
-        <v>1</v>
-      </c>
-      <c r="O13" s="12">
-        <v>1</v>
-      </c>
-      <c r="P13" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="14">
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="13">
+        <v>1</v>
+      </c>
+      <c r="L13" s="12">
+        <v>1</v>
+      </c>
+      <c r="M13" s="13">
+        <v>1</v>
+      </c>
+      <c r="N13" s="11">
+        <v>1</v>
+      </c>
+      <c r="O13" s="13">
+        <v>1</v>
+      </c>
+      <c r="P13" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A14" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="A14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="13">
         <v>9</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="12">
         <v>10</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <v>10</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="11">
         <v>6</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="11">
         <v>5</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="12">
         <v>4</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="12">
         <v>4</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="12">
-        <v>1</v>
-      </c>
-      <c r="L14" s="11">
-        <v>1</v>
-      </c>
-      <c r="M14" s="12">
-        <v>1</v>
-      </c>
-      <c r="N14" s="10">
-        <v>1</v>
-      </c>
-      <c r="O14" s="12">
-        <v>1</v>
-      </c>
-      <c r="P14" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="14">
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="13">
+        <v>1</v>
+      </c>
+      <c r="L14" s="12">
+        <v>1</v>
+      </c>
+      <c r="M14" s="13">
+        <v>1</v>
+      </c>
+      <c r="N14" s="11">
+        <v>1</v>
+      </c>
+      <c r="O14" s="13">
+        <v>1</v>
+      </c>
+      <c r="P14" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="15" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A15" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="A15" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="13">
         <v>9</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="12">
         <v>10</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="13">
         <v>10</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="11">
         <v>6</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="11">
         <v>5</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="12">
         <v>4</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="12">
         <v>4</v>
       </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="12">
-        <v>1</v>
-      </c>
-      <c r="L15" s="11">
-        <v>1</v>
-      </c>
-      <c r="M15" s="12">
-        <v>1</v>
-      </c>
-      <c r="N15" s="10">
-        <v>1</v>
-      </c>
-      <c r="O15" s="12">
-        <v>1</v>
-      </c>
-      <c r="P15" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="14">
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="13">
+        <v>1</v>
+      </c>
+      <c r="L15" s="12">
+        <v>1</v>
+      </c>
+      <c r="M15" s="13">
+        <v>1</v>
+      </c>
+      <c r="N15" s="11">
+        <v>1</v>
+      </c>
+      <c r="O15" s="13">
+        <v>1</v>
+      </c>
+      <c r="P15" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="33.95" customHeight="1" spans="1:23">
-      <c r="R16" s="15"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="W16" s="16"/>
+      <c r="R16" s="14"/>
+      <c r="T16" s="15"/>
+      <c r="U16" s="15"/>
+      <c r="W16" s="15"/>
     </row>
     <row r="17" ht="33.95" customHeight="1" spans="18:18">
-      <c r="R17" s="15"/>
+      <c r="R17" s="14"/>
     </row>
     <row r="18" ht="33.95" customHeight="1" spans="18:18">
-      <c r="R18" s="15"/>
+      <c r="R18" s="14"/>
     </row>
     <row r="19" ht="33.95" customHeight="1"/>
     <row r="20" ht="33.95" customHeight="1"/>
@@ -3130,8 +3161,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" outlineLevelCol="7"/>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="15.2857142857143" customWidth="1"/>
@@ -3139,41 +3170,41 @@
     <col min="4" max="8" width="11.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:8">
+    <row r="1" ht="15" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" ht="21" customHeight="1" spans="1:8">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" ht="21" customHeight="1" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -3181,43 +3212,49 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" ht="21" customHeight="1" spans="1:8">
+    <row r="3" ht="21" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-    </row>
-    <row r="4" ht="21" customHeight="1" spans="1:8">
-      <c r="A4" s="5"/>
+      <c r="L3" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1" spans="1:12">
+      <c r="A4" s="6"/>
       <c r="B4" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-    </row>
-    <row r="5" ht="21" customHeight="1" spans="1:8">
-      <c r="A5" s="5"/>
+      <c r="L4" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1" spans="1:12">
+      <c r="A5" s="6"/>
       <c r="B5" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -3225,13 +3262,13 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" ht="21" customHeight="1" spans="1:8">
-      <c r="A6" s="5"/>
+    <row r="6" ht="21" customHeight="1" spans="1:12">
+      <c r="A6" s="6"/>
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -3239,15 +3276,15 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" ht="21" customHeight="1" spans="1:8">
+    <row r="7" ht="21" customHeight="1" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -3255,13 +3292,13 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" ht="21" customHeight="1" spans="1:8">
-      <c r="A8" s="5"/>
+    <row r="8" ht="21" customHeight="1" spans="1:12">
+      <c r="A8" s="6"/>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -3269,13 +3306,13 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" ht="21" customHeight="1" spans="1:8">
-      <c r="A9" s="5"/>
+    <row r="9" ht="21" customHeight="1" spans="1:12">
+      <c r="A9" s="6"/>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -3283,13 +3320,13 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" ht="21" customHeight="1" spans="1:8">
-      <c r="A10" s="5"/>
+    <row r="10" ht="21" customHeight="1" spans="1:12">
+      <c r="A10" s="6"/>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -3297,15 +3334,15 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" ht="21" customHeight="1" spans="1:8">
+    <row r="11" ht="21" customHeight="1" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -3313,13 +3350,13 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" ht="21" customHeight="1" spans="1:8">
-      <c r="A12" s="5"/>
+    <row r="12" ht="21" customHeight="1" spans="1:12">
+      <c r="A12" s="6"/>
       <c r="B12" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -3327,13 +3364,13 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" ht="21" customHeight="1" spans="1:8">
-      <c r="A13" s="5"/>
+    <row r="13" ht="21" customHeight="1" spans="1:12">
+      <c r="A13" s="6"/>
       <c r="B13" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>

--- a/基本数据.xlsx
+++ b/基本数据.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\paike\github_upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup\Documents\paike\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="各班任课" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="113">
   <si>
     <t>班级</t>
   </si>
@@ -116,9 +116,6 @@
     <t>张懿</t>
   </si>
   <si>
-    <t>说明：班级名格式要统一，支持701班，七一班，七(1)班，七年级1班等</t>
-  </si>
-  <si>
     <t>七二班</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
     <t>李非非</t>
   </si>
   <si>
-    <t>班级没有的课程留空</t>
-  </si>
-  <si>
     <t>七三班</t>
   </si>
   <si>
@@ -275,9 +269,6 @@
     <t>九四班</t>
   </si>
   <si>
-    <t>说明：班级名格式要统一。支持701班，七一班，七(1)班，七年级1班等格式</t>
-  </si>
-  <si>
     <t>时间段</t>
   </si>
   <si>
@@ -320,16 +311,10 @@
     <t>第2节</t>
   </si>
   <si>
-    <t>说明：可以增减节次，也可以增加星期，比如有的学校周六、周天也上课，也是可以的。如果有一个或多个班周六也上课</t>
-  </si>
-  <si>
     <t>09:05-09:45</t>
   </si>
   <si>
     <t>第3节</t>
-  </si>
-  <si>
-    <t>，那么上课的星期数请增至星期六，总之取最多上课天数。</t>
   </si>
   <si>
     <t>10:15-10:55</t>
@@ -402,7 +387,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -428,13 +413,6 @@
       <color rgb="FF080000"/>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -983,155 +961,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1147,19 +1125,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1169,34 +1147,37 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1537,787 +1518,781 @@
   <dimension ref="A1:X30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="18.2571428571429" style="7" customWidth="1"/>
-    <col min="2" max="17" width="8.42857142857143" style="7" customWidth="1"/>
-    <col min="18" max="18" width="8.85714285714286" style="7" customWidth="1"/>
-    <col min="19" max="19" width="8.57142857142857" style="7" customWidth="1"/>
-    <col min="20" max="16384" width="9.14285714285714" style="7"/>
+    <col min="1" max="1" width="18.2571428571429" style="6" customWidth="1"/>
+    <col min="2" max="17" width="8.42857142857143" style="6" customWidth="1"/>
+    <col min="18" max="18" width="8.85714285714286" style="6" customWidth="1"/>
+    <col min="19" max="19" width="8.57142857142857" style="6" customWidth="1"/>
+    <col min="20" max="16384" width="9.14285714285714" style="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="46.5" customHeight="1" spans="1:24">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="Q2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="5" t="s">
+    </row>
+    <row r="3" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A3" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A3" s="10" t="s">
+      <c r="B3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="D3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="M3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q6" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q7" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12" t="s">
+      <c r="F8" s="10"/>
+      <c r="G8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A10" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="P12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q13" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H14" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="P14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" ht="35.1" customHeight="1" spans="1:24">
+      <c r="A15" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="13" t="s">
+      <c r="D15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A6" s="10" t="s">
+      <c r="L15" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q6" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A7" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12" t="s">
+      <c r="Q15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="P7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q7" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A8" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="P8" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A9" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q9" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A10" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q10" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="P11" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A12" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q12" s="16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A13" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="P13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A14" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="P14" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q14" s="18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" ht="35.1" customHeight="1" spans="1:24">
-      <c r="A15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="P15" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q15" s="16" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="16" ht="33.95" customHeight="1" spans="1:24">
-      <c r="R16" s="20"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="22"/>
+      <c r="R16" s="21"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="23"/>
     </row>
     <row r="17" ht="33.95" customHeight="1" spans="18:23">
-      <c r="R17" s="14"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="W17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="W17" s="16"/>
     </row>
     <row r="18" ht="33.95" customHeight="1" spans="18:23">
-      <c r="R18" s="14"/>
+      <c r="R18" s="15"/>
     </row>
     <row r="19" ht="33.95" customHeight="1" spans="18:23">
-      <c r="R19" s="14"/>
+      <c r="R19" s="15"/>
     </row>
     <row r="20" ht="33.95" customHeight="1"/>
     <row r="21" ht="33.95" customHeight="1"/>
@@ -2356,779 +2331,773 @@
   <dimension ref="A1:W29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="18.2571428571429" style="7" customWidth="1"/>
-    <col min="2" max="17" width="8.42857142857143" style="7" customWidth="1"/>
-    <col min="18" max="18" width="8.85714285714286" style="7" customWidth="1"/>
-    <col min="19" max="19" width="8.57142857142857" style="7" customWidth="1"/>
-    <col min="20" max="16384" width="9.14285714285714" style="7"/>
+    <col min="1" max="1" width="18.2571428571429" style="6" customWidth="1"/>
+    <col min="2" max="17" width="8.42857142857143" style="6" customWidth="1"/>
+    <col min="18" max="18" width="8.85714285714286" style="6" customWidth="1"/>
+    <col min="19" max="19" width="8.57142857142857" style="6" customWidth="1"/>
+    <col min="20" max="16384" width="9.14285714285714" style="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="46.5" customHeight="1" spans="1:23">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>11</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>12</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>12</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11">
-        <v>3</v>
-      </c>
-      <c r="H2" s="12">
-        <v>3</v>
-      </c>
-      <c r="I2" s="13">
-        <v>3</v>
-      </c>
-      <c r="J2" s="13">
-        <v>3</v>
-      </c>
-      <c r="K2" s="13">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <v>3</v>
+      </c>
+      <c r="H2" s="11">
+        <v>3</v>
+      </c>
+      <c r="I2" s="12">
+        <v>3</v>
+      </c>
+      <c r="J2" s="12">
+        <v>3</v>
+      </c>
+      <c r="K2" s="12">
         <v>2</v>
       </c>
-      <c r="L2" s="12">
-        <v>1</v>
-      </c>
-      <c r="M2" s="11">
-        <v>1</v>
-      </c>
-      <c r="N2" s="12">
-        <v>1</v>
-      </c>
-      <c r="O2" s="11">
-        <v>1</v>
-      </c>
-      <c r="P2" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="11">
-        <v>1</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>79</v>
+      <c r="L2" s="11">
+        <v>1</v>
+      </c>
+      <c r="M2" s="10">
+        <v>1</v>
+      </c>
+      <c r="N2" s="11">
+        <v>1</v>
+      </c>
+      <c r="O2" s="10">
+        <v>1</v>
+      </c>
+      <c r="P2" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A3" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="11">
+      <c r="A3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="10">
         <v>11</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <v>12</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>12</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11">
-        <v>3</v>
-      </c>
-      <c r="H3" s="12">
-        <v>3</v>
-      </c>
-      <c r="I3" s="13">
-        <v>3</v>
-      </c>
-      <c r="J3" s="13">
-        <v>3</v>
-      </c>
-      <c r="K3" s="13">
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10">
+        <v>3</v>
+      </c>
+      <c r="H3" s="11">
+        <v>3</v>
+      </c>
+      <c r="I3" s="12">
+        <v>3</v>
+      </c>
+      <c r="J3" s="12">
+        <v>3</v>
+      </c>
+      <c r="K3" s="12">
         <v>2</v>
       </c>
-      <c r="L3" s="12">
-        <v>1</v>
-      </c>
-      <c r="M3" s="11">
-        <v>1</v>
-      </c>
-      <c r="N3" s="12">
-        <v>1</v>
-      </c>
-      <c r="O3" s="11">
-        <v>1</v>
-      </c>
-      <c r="P3" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>1</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>31</v>
+      <c r="L3" s="11">
+        <v>1</v>
+      </c>
+      <c r="M3" s="10">
+        <v>1</v>
+      </c>
+      <c r="N3" s="11">
+        <v>1</v>
+      </c>
+      <c r="O3" s="10">
+        <v>1</v>
+      </c>
+      <c r="P3" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="11">
+      <c r="A4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="10">
         <v>11</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>12</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>12</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11">
-        <v>3</v>
-      </c>
-      <c r="H4" s="12">
-        <v>3</v>
-      </c>
-      <c r="I4" s="13">
-        <v>3</v>
-      </c>
-      <c r="J4" s="13">
-        <v>3</v>
-      </c>
-      <c r="K4" s="13">
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10">
+        <v>3</v>
+      </c>
+      <c r="H4" s="11">
+        <v>3</v>
+      </c>
+      <c r="I4" s="12">
+        <v>3</v>
+      </c>
+      <c r="J4" s="12">
+        <v>3</v>
+      </c>
+      <c r="K4" s="12">
         <v>2</v>
       </c>
-      <c r="L4" s="12">
-        <v>1</v>
-      </c>
-      <c r="M4" s="11">
-        <v>1</v>
-      </c>
-      <c r="N4" s="12">
-        <v>1</v>
-      </c>
-      <c r="O4" s="11">
-        <v>1</v>
-      </c>
-      <c r="P4" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="11">
+      <c r="L4" s="11">
+        <v>1</v>
+      </c>
+      <c r="M4" s="10">
+        <v>1</v>
+      </c>
+      <c r="N4" s="11">
+        <v>1</v>
+      </c>
+      <c r="O4" s="10">
+        <v>1</v>
+      </c>
+      <c r="P4" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="11">
+      <c r="A5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="10">
         <v>11</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>12</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>12</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11">
-        <v>3</v>
-      </c>
-      <c r="H5" s="12">
-        <v>3</v>
-      </c>
-      <c r="I5" s="13">
-        <v>3</v>
-      </c>
-      <c r="J5" s="13">
-        <v>3</v>
-      </c>
-      <c r="K5" s="13">
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10">
+        <v>3</v>
+      </c>
+      <c r="H5" s="11">
+        <v>3</v>
+      </c>
+      <c r="I5" s="12">
+        <v>3</v>
+      </c>
+      <c r="J5" s="12">
+        <v>3</v>
+      </c>
+      <c r="K5" s="12">
         <v>2</v>
       </c>
-      <c r="L5" s="12">
-        <v>1</v>
-      </c>
-      <c r="M5" s="11">
-        <v>1</v>
-      </c>
-      <c r="N5" s="12">
-        <v>1</v>
-      </c>
-      <c r="O5" s="11">
-        <v>1</v>
-      </c>
-      <c r="P5" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="11">
+      <c r="L5" s="11">
+        <v>1</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1</v>
+      </c>
+      <c r="N5" s="11">
+        <v>1</v>
+      </c>
+      <c r="O5" s="10">
+        <v>1</v>
+      </c>
+      <c r="P5" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="11">
+      <c r="A6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="10">
         <v>11</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>12</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>12</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11">
-        <v>3</v>
-      </c>
-      <c r="H6" s="12">
-        <v>3</v>
-      </c>
-      <c r="I6" s="13">
-        <v>3</v>
-      </c>
-      <c r="J6" s="13">
-        <v>3</v>
-      </c>
-      <c r="K6" s="13">
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10">
+        <v>3</v>
+      </c>
+      <c r="H6" s="11">
+        <v>3</v>
+      </c>
+      <c r="I6" s="12">
+        <v>3</v>
+      </c>
+      <c r="J6" s="12">
+        <v>3</v>
+      </c>
+      <c r="K6" s="12">
         <v>2</v>
       </c>
-      <c r="L6" s="12">
-        <v>1</v>
-      </c>
-      <c r="M6" s="11">
-        <v>1</v>
-      </c>
-      <c r="N6" s="12">
-        <v>1</v>
-      </c>
-      <c r="O6" s="11">
-        <v>1</v>
-      </c>
-      <c r="P6" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="11">
+      <c r="L6" s="11">
+        <v>1</v>
+      </c>
+      <c r="M6" s="10">
+        <v>1</v>
+      </c>
+      <c r="N6" s="11">
+        <v>1</v>
+      </c>
+      <c r="O6" s="10">
+        <v>1</v>
+      </c>
+      <c r="P6" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A7" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="11">
+      <c r="A7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="10">
         <v>9</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <v>10</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>10</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>6</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12">
-        <v>3</v>
-      </c>
-      <c r="H7" s="12">
-        <v>3</v>
-      </c>
-      <c r="I7" s="13">
-        <v>3</v>
-      </c>
-      <c r="J7" s="13">
-        <v>3</v>
-      </c>
-      <c r="K7" s="13">
+      <c r="F7" s="10"/>
+      <c r="G7" s="11">
+        <v>3</v>
+      </c>
+      <c r="H7" s="11">
+        <v>3</v>
+      </c>
+      <c r="I7" s="12">
+        <v>3</v>
+      </c>
+      <c r="J7" s="12">
+        <v>3</v>
+      </c>
+      <c r="K7" s="12">
         <v>2</v>
       </c>
-      <c r="L7" s="12">
-        <v>1</v>
-      </c>
-      <c r="M7" s="11">
-        <v>1</v>
-      </c>
-      <c r="N7" s="12">
-        <v>1</v>
-      </c>
-      <c r="O7" s="11">
-        <v>1</v>
-      </c>
-      <c r="P7" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="11">
+      <c r="L7" s="11">
+        <v>1</v>
+      </c>
+      <c r="M7" s="10">
+        <v>1</v>
+      </c>
+      <c r="N7" s="11">
+        <v>1</v>
+      </c>
+      <c r="O7" s="10">
+        <v>1</v>
+      </c>
+      <c r="P7" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A8" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="11">
+      <c r="A8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="10">
         <v>9</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>10</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>10</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>6</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12">
-        <v>3</v>
-      </c>
-      <c r="H8" s="12">
-        <v>3</v>
-      </c>
-      <c r="I8" s="13">
-        <v>3</v>
-      </c>
-      <c r="J8" s="13">
-        <v>3</v>
-      </c>
-      <c r="K8" s="13">
+      <c r="F8" s="10"/>
+      <c r="G8" s="11">
+        <v>3</v>
+      </c>
+      <c r="H8" s="11">
+        <v>3</v>
+      </c>
+      <c r="I8" s="12">
+        <v>3</v>
+      </c>
+      <c r="J8" s="12">
+        <v>3</v>
+      </c>
+      <c r="K8" s="12">
         <v>2</v>
       </c>
-      <c r="L8" s="12">
-        <v>1</v>
-      </c>
-      <c r="M8" s="11">
-        <v>1</v>
-      </c>
-      <c r="N8" s="12">
-        <v>1</v>
-      </c>
-      <c r="O8" s="11">
-        <v>1</v>
-      </c>
-      <c r="P8" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="11">
+      <c r="L8" s="11">
+        <v>1</v>
+      </c>
+      <c r="M8" s="10">
+        <v>1</v>
+      </c>
+      <c r="N8" s="11">
+        <v>1</v>
+      </c>
+      <c r="O8" s="10">
+        <v>1</v>
+      </c>
+      <c r="P8" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A9" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="11">
+      <c r="A9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="10">
         <v>9</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <v>10</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>10</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>6</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12">
-        <v>3</v>
-      </c>
-      <c r="H9" s="12">
-        <v>3</v>
-      </c>
-      <c r="I9" s="13">
-        <v>3</v>
-      </c>
-      <c r="J9" s="13">
-        <v>3</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="F9" s="10"/>
+      <c r="G9" s="11">
+        <v>3</v>
+      </c>
+      <c r="H9" s="11">
+        <v>3</v>
+      </c>
+      <c r="I9" s="12">
+        <v>3</v>
+      </c>
+      <c r="J9" s="12">
+        <v>3</v>
+      </c>
+      <c r="K9" s="12">
         <v>2</v>
       </c>
-      <c r="L9" s="12">
-        <v>1</v>
-      </c>
-      <c r="M9" s="11">
-        <v>1</v>
-      </c>
-      <c r="N9" s="12">
-        <v>1</v>
-      </c>
-      <c r="O9" s="11">
-        <v>1</v>
-      </c>
-      <c r="P9" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="11">
+      <c r="L9" s="11">
+        <v>1</v>
+      </c>
+      <c r="M9" s="10">
+        <v>1</v>
+      </c>
+      <c r="N9" s="11">
+        <v>1</v>
+      </c>
+      <c r="O9" s="10">
+        <v>1</v>
+      </c>
+      <c r="P9" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A10" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="11">
+      <c r="A10" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="10">
         <v>9</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <v>10</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>10</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>6</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12">
-        <v>3</v>
-      </c>
-      <c r="H10" s="12">
-        <v>3</v>
-      </c>
-      <c r="I10" s="13">
-        <v>3</v>
-      </c>
-      <c r="J10" s="13">
-        <v>3</v>
-      </c>
-      <c r="K10" s="13">
+      <c r="F10" s="10"/>
+      <c r="G10" s="11">
+        <v>3</v>
+      </c>
+      <c r="H10" s="11">
+        <v>3</v>
+      </c>
+      <c r="I10" s="12">
+        <v>3</v>
+      </c>
+      <c r="J10" s="12">
+        <v>3</v>
+      </c>
+      <c r="K10" s="12">
         <v>2</v>
       </c>
-      <c r="L10" s="12">
-        <v>1</v>
-      </c>
-      <c r="M10" s="11">
-        <v>1</v>
-      </c>
-      <c r="N10" s="12">
-        <v>1</v>
-      </c>
-      <c r="O10" s="11">
-        <v>1</v>
-      </c>
-      <c r="P10" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="11">
+      <c r="L10" s="11">
+        <v>1</v>
+      </c>
+      <c r="M10" s="10">
+        <v>1</v>
+      </c>
+      <c r="N10" s="11">
+        <v>1</v>
+      </c>
+      <c r="O10" s="10">
+        <v>1</v>
+      </c>
+      <c r="P10" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="11">
+      <c r="A11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="10">
         <v>9</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>10</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>10</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <v>6</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12">
-        <v>3</v>
-      </c>
-      <c r="H11" s="12">
-        <v>3</v>
-      </c>
-      <c r="I11" s="13">
-        <v>3</v>
-      </c>
-      <c r="J11" s="13">
-        <v>3</v>
-      </c>
-      <c r="K11" s="13">
+      <c r="F11" s="10"/>
+      <c r="G11" s="11">
+        <v>3</v>
+      </c>
+      <c r="H11" s="11">
+        <v>3</v>
+      </c>
+      <c r="I11" s="12">
+        <v>3</v>
+      </c>
+      <c r="J11" s="12">
+        <v>3</v>
+      </c>
+      <c r="K11" s="12">
         <v>2</v>
       </c>
-      <c r="L11" s="12">
-        <v>1</v>
-      </c>
-      <c r="M11" s="11">
-        <v>1</v>
-      </c>
-      <c r="N11" s="12">
-        <v>1</v>
-      </c>
-      <c r="O11" s="11">
-        <v>1</v>
-      </c>
-      <c r="P11" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="11">
+      <c r="L11" s="11">
+        <v>1</v>
+      </c>
+      <c r="M11" s="10">
+        <v>1</v>
+      </c>
+      <c r="N11" s="11">
+        <v>1</v>
+      </c>
+      <c r="O11" s="10">
+        <v>1</v>
+      </c>
+      <c r="P11" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="12" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="12">
+        <v>9</v>
+      </c>
+      <c r="C12" s="11">
+        <v>10</v>
+      </c>
+      <c r="D12" s="12">
+        <v>10</v>
+      </c>
+      <c r="E12" s="10">
+        <v>6</v>
+      </c>
+      <c r="F12" s="10">
+        <v>5</v>
+      </c>
+      <c r="G12" s="11">
+        <v>4</v>
+      </c>
+      <c r="H12" s="11">
+        <v>4</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="11">
+        <v>1</v>
+      </c>
+      <c r="M12" s="12">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10">
+        <v>1</v>
+      </c>
+      <c r="O12" s="12">
+        <v>1</v>
+      </c>
+      <c r="P12" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="35.1" customHeight="1" spans="1:23">
+      <c r="A13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B13" s="12">
         <v>9</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C13" s="11">
         <v>10</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D13" s="12">
         <v>10</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E13" s="10">
         <v>6</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F13" s="10">
         <v>5</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G13" s="11">
         <v>4</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H13" s="11">
         <v>4</v>
       </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="13">
-        <v>1</v>
-      </c>
-      <c r="L12" s="12">
-        <v>1</v>
-      </c>
-      <c r="M12" s="13">
-        <v>1</v>
-      </c>
-      <c r="N12" s="11">
-        <v>1</v>
-      </c>
-      <c r="O12" s="13">
-        <v>1</v>
-      </c>
-      <c r="P12" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A13" s="10" t="s">
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="12">
+        <v>1</v>
+      </c>
+      <c r="L13" s="11">
+        <v>1</v>
+      </c>
+      <c r="M13" s="12">
+        <v>1</v>
+      </c>
+      <c r="N13" s="10">
+        <v>1</v>
+      </c>
+      <c r="O13" s="12">
+        <v>1</v>
+      </c>
+      <c r="P13" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="35.1" customHeight="1" spans="1:23">
+      <c r="A14" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B14" s="12">
         <v>9</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C14" s="11">
         <v>10</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D14" s="12">
         <v>10</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E14" s="10">
         <v>6</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F14" s="10">
         <v>5</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G14" s="11">
         <v>4</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H14" s="11">
         <v>4</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="13">
-        <v>1</v>
-      </c>
-      <c r="L13" s="12">
-        <v>1</v>
-      </c>
-      <c r="M13" s="13">
-        <v>1</v>
-      </c>
-      <c r="N13" s="11">
-        <v>1</v>
-      </c>
-      <c r="O13" s="13">
-        <v>1</v>
-      </c>
-      <c r="P13" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A14" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="12">
+        <v>1</v>
+      </c>
+      <c r="L14" s="11">
+        <v>1</v>
+      </c>
+      <c r="M14" s="12">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10">
+        <v>1</v>
+      </c>
+      <c r="O14" s="12">
+        <v>1</v>
+      </c>
+      <c r="P14" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="35.1" customHeight="1" spans="1:23">
+      <c r="A15" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="12">
         <v>9</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C15" s="11">
         <v>10</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D15" s="12">
         <v>10</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E15" s="10">
         <v>6</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F15" s="10">
         <v>5</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G15" s="11">
         <v>4</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H15" s="11">
         <v>4</v>
       </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="13">
-        <v>1</v>
-      </c>
-      <c r="L14" s="12">
-        <v>1</v>
-      </c>
-      <c r="M14" s="13">
-        <v>1</v>
-      </c>
-      <c r="N14" s="11">
-        <v>1</v>
-      </c>
-      <c r="O14" s="13">
-        <v>1</v>
-      </c>
-      <c r="P14" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="35.1" customHeight="1" spans="1:23">
-      <c r="A15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="13">
-        <v>9</v>
-      </c>
-      <c r="C15" s="12">
-        <v>10</v>
-      </c>
-      <c r="D15" s="13">
-        <v>10</v>
-      </c>
-      <c r="E15" s="11">
-        <v>6</v>
-      </c>
-      <c r="F15" s="11">
-        <v>5</v>
-      </c>
-      <c r="G15" s="12">
-        <v>4</v>
-      </c>
-      <c r="H15" s="12">
-        <v>4</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="13">
-        <v>1</v>
-      </c>
-      <c r="L15" s="12">
-        <v>1</v>
-      </c>
-      <c r="M15" s="13">
-        <v>1</v>
-      </c>
-      <c r="N15" s="11">
-        <v>1</v>
-      </c>
-      <c r="O15" s="13">
-        <v>1</v>
-      </c>
-      <c r="P15" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="12">
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="12">
+        <v>1</v>
+      </c>
+      <c r="L15" s="11">
+        <v>1</v>
+      </c>
+      <c r="M15" s="12">
+        <v>1</v>
+      </c>
+      <c r="N15" s="10">
+        <v>1</v>
+      </c>
+      <c r="O15" s="12">
+        <v>1</v>
+      </c>
+      <c r="P15" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="33.95" customHeight="1" spans="1:23">
-      <c r="R16" s="14"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="W16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="W16" s="16"/>
     </row>
     <row r="17" ht="33.95" customHeight="1" spans="18:18">
-      <c r="R17" s="14"/>
+      <c r="R17" s="15"/>
     </row>
     <row r="18" ht="33.95" customHeight="1" spans="18:18">
-      <c r="R18" s="14"/>
+      <c r="R18" s="15"/>
     </row>
     <row r="19" ht="33.95" customHeight="1"/>
     <row r="20" ht="33.95" customHeight="1"/>
@@ -3161,8 +3130,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="15.2857142857143" customWidth="1"/>
@@ -3170,41 +3139,41 @@
     <col min="4" max="8" width="11.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:12">
+    <row r="1" ht="15" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" ht="21" customHeight="1" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="2" ht="21" customHeight="1" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -3212,49 +3181,43 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" ht="21" customHeight="1" spans="1:12">
+    <row r="3" ht="21" customHeight="1" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="L3" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" ht="21" customHeight="1" spans="1:12">
-      <c r="A4" s="6"/>
+    </row>
+    <row r="4" ht="21" customHeight="1" spans="1:8">
+      <c r="A4" s="5"/>
       <c r="B4" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="L4" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" ht="21" customHeight="1" spans="1:12">
-      <c r="A5" s="6"/>
+    </row>
+    <row r="5" ht="21" customHeight="1" spans="1:8">
+      <c r="A5" s="5"/>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -3262,13 +3225,13 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" ht="21" customHeight="1" spans="1:12">
-      <c r="A6" s="6"/>
+    <row r="6" ht="21" customHeight="1" spans="1:8">
+      <c r="A6" s="5"/>
       <c r="B6" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -3276,15 +3239,15 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" ht="21" customHeight="1" spans="1:12">
+    <row r="7" ht="21" customHeight="1" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -3292,13 +3255,13 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" ht="21" customHeight="1" spans="1:12">
-      <c r="A8" s="6"/>
+    <row r="8" ht="21" customHeight="1" spans="1:8">
+      <c r="A8" s="5"/>
       <c r="B8" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -3306,13 +3269,13 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" ht="21" customHeight="1" spans="1:12">
-      <c r="A9" s="6"/>
+    <row r="9" ht="21" customHeight="1" spans="1:8">
+      <c r="A9" s="5"/>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -3320,13 +3283,13 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" ht="21" customHeight="1" spans="1:12">
-      <c r="A10" s="6"/>
+    <row r="10" ht="21" customHeight="1" spans="1:8">
+      <c r="A10" s="5"/>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -3334,15 +3297,15 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" ht="21" customHeight="1" spans="1:12">
+    <row r="11" ht="21" customHeight="1" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -3350,13 +3313,13 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" ht="21" customHeight="1" spans="1:12">
-      <c r="A12" s="6"/>
+    <row r="12" ht="21" customHeight="1" spans="1:8">
+      <c r="A12" s="5"/>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -3364,13 +3327,13 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" ht="21" customHeight="1" spans="1:12">
-      <c r="A13" s="6"/>
+    <row r="13" ht="21" customHeight="1" spans="1:8">
+      <c r="A13" s="5"/>
       <c r="B13" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
